--- a/Excel/Datas/card_effect.xlsx
+++ b/Excel/Datas/card_effect.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28227"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Project-SS\Excel\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9EE9238-F374-4DB2-B1DE-85E195767EB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4455" yWindow="5895" windowWidth="15540" windowHeight="12930" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="30240" windowHeight="12920"/>
   </bookViews>
   <sheets>
     <sheet name="card_effect_table" sheetId="1" r:id="rId1"/>
@@ -24,6 +18,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -31,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="58">
   <si>
     <t>##var</t>
   </si>
@@ -39,12 +35,63 @@
     <t>id</t>
   </si>
   <si>
+    <t>needTarget</t>
+  </si>
+  <si>
+    <t>targetGroup</t>
+  </si>
+  <si>
+    <t>matchRace</t>
+  </si>
+  <si>
+    <t>buffListWhenMatchRace1</t>
+  </si>
+  <si>
+    <t>buffParamListWhenMatchRace1</t>
+  </si>
+  <si>
+    <t>buffListWhenMissMatchRace1</t>
+  </si>
+  <si>
+    <t>buffParamListWhenMissMatchRace1</t>
+  </si>
+  <si>
+    <t>matchGroup</t>
+  </si>
+  <si>
+    <t>buffListWhenMatchGroup1</t>
+  </si>
+  <si>
+    <t>buffParamListWhenMatchGroup1</t>
+  </si>
+  <si>
+    <t>buffListWhenDissMatchGroup1</t>
+  </si>
+  <si>
+    <t>buffParamListWhenDissMatchGroup1</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
     <t>ItemEnum</t>
   </si>
   <si>
+    <t>bool</t>
+  </si>
+  <si>
+    <t>GroupEnum</t>
+  </si>
+  <si>
+    <t>RaceEnum</t>
+  </si>
+  <si>
+    <t>(list#sep=,),BuffEnum</t>
+  </si>
+  <si>
+    <t>(list#sep=,),float</t>
+  </si>
+  <si>
     <t>##group</t>
   </si>
   <si>
@@ -54,26 +101,119 @@
     <t>ID</t>
   </si>
   <si>
+    <t>是否拖到某个目标上使用</t>
+  </si>
+  <si>
+    <t>目标方阵营</t>
+  </si>
+  <si>
+    <t>匹配的目标种族</t>
+  </si>
+  <si>
+    <t>当种族匹配时给的Buff</t>
+  </si>
+  <si>
+    <t>当种族匹配时给的Buff的参数</t>
+  </si>
+  <si>
+    <t>当种族不匹配时给的Buff</t>
+  </si>
+  <si>
+    <t>当种族不匹配时给的Buff的参数1</t>
+  </si>
+  <si>
+    <t>匹配的目标阵营</t>
+  </si>
+  <si>
+    <t>目标阵匹配时给的Buff</t>
+  </si>
+  <si>
+    <t>目标阵匹配时给的Buff的参数</t>
+  </si>
+  <si>
+    <t>目标阵营不匹配时给的Buff</t>
+  </si>
+  <si>
+    <t>目标阵营不匹配时给的Buff的参数</t>
+  </si>
+  <si>
     <t>高速升级</t>
   </si>
   <si>
+    <t>友方</t>
+  </si>
+  <si>
+    <t>机械</t>
+  </si>
+  <si>
+    <t>永久速度</t>
+  </si>
+  <si>
+    <t>2,</t>
+  </si>
+  <si>
+    <t>临时固定速度</t>
+  </si>
+  <si>
     <t>装甲升级</t>
   </si>
   <si>
+    <t>永久固定防御力,永久固定力量</t>
+  </si>
+  <si>
+    <t>1,1</t>
+  </si>
+  <si>
+    <t>临时固定力量,临时固定防御</t>
+  </si>
+  <si>
+    <t>10,10</t>
+  </si>
+  <si>
     <t>重组升级</t>
   </si>
   <si>
+    <t>永久固定生命值</t>
+  </si>
+  <si>
+    <t>恢复百分比生命</t>
+  </si>
+  <si>
     <t>能量饮料</t>
   </si>
   <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>下次攻击伤害倍率,下次攻击伤害倍率,下次攻击伤害倍率</t>
+  </si>
+  <si>
+    <t>3,3,3</t>
+  </si>
+  <si>
+    <t>降低百分比力量</t>
+  </si>
+  <si>
     <t>脏拖把</t>
+  </si>
+  <si>
+    <t>敌方</t>
+  </si>
+  <si>
+    <t>受到固定真实伤害</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -96,13 +236,151 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -111,13 +389,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79961546678060247"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39960936307870726"/>
+        <fgColor theme="5" tint="0.799615466780602"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399609363078707"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -127,8 +405,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -194,53 +658,354 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FFF43308"/>
-      <color rgb="FFFF8680"/>
+      <color rgb="00F43308"/>
+      <color rgb="00FF8680"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -498,215 +1263,476 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:O20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="2" max="2" width="18.5" customWidth="1"/>
-    <col min="3" max="4" width="21.625" customWidth="1"/>
-    <col min="5" max="8" width="13.5" customWidth="1"/>
+    <col min="3" max="3" width="22.7589285714286" customWidth="1"/>
+    <col min="4" max="4" width="21.625" customWidth="1"/>
+    <col min="5" max="7" width="27.6696428571429" style="1" customWidth="1"/>
+    <col min="8" max="8" width="30.6517857142857" style="1" customWidth="1"/>
+    <col min="9" max="9" width="26.9285714285714" style="1" customWidth="1"/>
+    <col min="10" max="10" width="13.5" customWidth="1"/>
+    <col min="11" max="11" width="22.0178571428571" customWidth="1"/>
+    <col min="12" max="12" width="19.9375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="22.4642857142857" customWidth="1"/>
+    <col min="14" max="15" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:15">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="2"/>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="2"/>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="O3" s="2"/>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="2"/>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="M5" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="N5" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="O5" s="13"/>
+    </row>
+    <row r="6" ht="17.55" spans="2:15">
+      <c r="B6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" s="11">
+        <v>10</v>
+      </c>
+      <c r="J6" s="14"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="11"/>
+      <c r="O6" s="4"/>
+    </row>
+    <row r="7" ht="17.55" spans="2:15">
+      <c r="B7" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" t="b">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="J7" s="14"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="4"/>
+    </row>
+    <row r="8" ht="17.55" spans="2:15">
+      <c r="B8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" s="10">
         <v>5</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B9" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B10" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B18" s="5"/>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B19" s="5"/>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B20" s="5"/>
+      <c r="H8" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="I8" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="J8" s="7"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="12"/>
+      <c r="O8" s="4"/>
+    </row>
+    <row r="9" ht="17.55" spans="2:15">
+      <c r="B9" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" t="b">
+        <v>1</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="J9" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="K9" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="M9" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="N9" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="O9" s="4"/>
+    </row>
+    <row r="10" ht="17.55" spans="2:15">
+      <c r="B10" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" t="b">
+        <v>1</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="I10" s="12">
+        <v>30</v>
+      </c>
+      <c r="J10" s="7"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="12"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="12"/>
+      <c r="O10" s="4"/>
+    </row>
+    <row r="11" ht="17.55" spans="2:15">
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="12"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+      <c r="O11" s="7"/>
+    </row>
+    <row r="12" ht="17.55" spans="2:15">
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="7"/>
+    </row>
+    <row r="13" ht="17.55" spans="2:15">
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="12"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+      <c r="O13" s="7"/>
+    </row>
+    <row r="14" ht="17.55" spans="2:15">
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="12"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
+      <c r="O14" s="7"/>
+    </row>
+    <row r="15" ht="17.55" spans="2:15">
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="7"/>
+    </row>
+    <row r="16" ht="17.55" spans="2:15">
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="12"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
+      <c r="O16" s="7"/>
+    </row>
+    <row r="17" ht="17.55" spans="2:15">
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="12"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
+      <c r="O17" s="7"/>
+    </row>
+    <row r="18" ht="17.55" spans="2:2">
+      <c r="B18" s="7"/>
+    </row>
+    <row r="19" ht="17.55" spans="2:2">
+      <c r="B19" s="7"/>
+    </row>
+    <row r="20" ht="17.55" spans="2:2">
+      <c r="B20" s="7"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Excel/Datas/card_effect.xlsx
+++ b/Excel/Datas/card_effect.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="62">
   <si>
     <t>##var</t>
   </si>
@@ -38,6 +38,9 @@
     <t>needTarget</t>
   </si>
   <si>
+    <t>targetType</t>
+  </si>
+  <si>
     <t>targetGroup</t>
   </si>
   <si>
@@ -80,6 +83,9 @@
     <t>bool</t>
   </si>
   <si>
+    <t>EntityTypeEnum</t>
+  </si>
+  <si>
     <t>GroupEnum</t>
   </si>
   <si>
@@ -104,6 +110,9 @@
     <t>是否拖到某个目标上使用</t>
   </si>
   <si>
+    <t>目标的类型</t>
+  </si>
+  <si>
     <t>目标方阵营</t>
   </si>
   <si>
@@ -140,6 +149,9 @@
     <t>高速升级</t>
   </si>
   <si>
+    <t>Pokemon</t>
+  </si>
+  <si>
     <t>友方</t>
   </si>
   <si>
@@ -182,7 +194,7 @@
     <t>能量饮料</t>
   </si>
   <si>
-    <t>All</t>
+    <t>敌我双方</t>
   </si>
   <si>
     <t>下次攻击伤害倍率,下次攻击伤害倍率,下次攻击伤害倍率</t>
@@ -380,7 +392,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -402,6 +414,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -780,7 +816,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -804,16 +840,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -822,25 +858,13 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -903,8 +927,20 @@
     <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -932,16 +968,58 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1269,23 +1347,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O20"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="2" max="2" width="18.5" customWidth="1"/>
     <col min="3" max="3" width="22.7589285714286" customWidth="1"/>
-    <col min="4" max="4" width="21.625" customWidth="1"/>
-    <col min="5" max="7" width="27.6696428571429" style="1" customWidth="1"/>
-    <col min="8" max="8" width="30.6517857142857" style="1" customWidth="1"/>
-    <col min="9" max="9" width="26.9285714285714" style="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5" customWidth="1"/>
-    <col min="11" max="11" width="22.0178571428571" customWidth="1"/>
-    <col min="12" max="12" width="19.9375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="22.4642857142857" customWidth="1"/>
-    <col min="14" max="15" width="13.5" customWidth="1"/>
+    <col min="4" max="5" width="21.625" customWidth="1"/>
+    <col min="6" max="8" width="27.6696428571429" style="1" customWidth="1"/>
+    <col min="9" max="9" width="30.6517857142857" style="1" customWidth="1"/>
+    <col min="10" max="10" width="26.9285714285714" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13.5" customWidth="1"/>
+    <col min="12" max="12" width="22.0178571428571" customWidth="1"/>
+    <col min="13" max="13" width="19.9375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="22.4642857142857" customWidth="1"/>
+    <col min="15" max="16" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:16">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1298,7 +1376,7 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="8" t="s">
@@ -1313,414 +1391,449 @@
       <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="8" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2"/>
-    </row>
-    <row r="2" spans="1:15">
+      <c r="O1" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2"/>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
-      <c r="E2" s="8"/>
+      <c r="E2" s="2"/>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
       <c r="H2" s="8"/>
       <c r="I2" s="8"/>
-      <c r="J2" s="2"/>
+      <c r="J2" s="8"/>
       <c r="K2" s="2"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="2"/>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="L2" s="2"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="2"/>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="8" t="s">
         <v>18</v>
       </c>
+      <c r="E3" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="F3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>19</v>
-      </c>
       <c r="L3" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="O3" s="2"/>
-    </row>
-    <row r="4" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O3" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P3" s="2"/>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
-      <c r="E4" s="8"/>
+      <c r="E4" s="2"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
       <c r="I4" s="8"/>
-      <c r="J4" s="2"/>
+      <c r="J4" s="8"/>
       <c r="K4" s="2"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="2"/>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="L4" s="2"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="2"/>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="J5" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="K5" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="L5" s="9" t="s">
+      <c r="J5" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="M5" s="13" t="s">
+      <c r="K5" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="N5" s="9" t="s">
+      <c r="L5" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="O5" s="13"/>
-    </row>
-    <row r="6" ht="17.55" spans="2:15">
+      <c r="M5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="N5" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="O5" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="P5" s="14"/>
+    </row>
+    <row r="6" ht="17.55" spans="2:16">
       <c r="B6" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C6" t="b">
         <v>1</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>38</v>
+        <v>40</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>41</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>40</v>
+        <v>42</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>43</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="I6" s="11">
+        <v>44</v>
+      </c>
+      <c r="I6" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="J6" s="15">
         <v>10</v>
       </c>
-      <c r="J6" s="14"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="11"/>
-      <c r="O6" s="4"/>
-    </row>
-    <row r="7" ht="17.55" spans="2:15">
+      <c r="K6" s="16"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="22"/>
+      <c r="N6" s="23"/>
+      <c r="O6" s="24"/>
+      <c r="P6" s="4"/>
+    </row>
+    <row r="7" ht="17.55" spans="2:16">
       <c r="B7" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C7" t="b">
         <v>1</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>38</v>
+        <v>40</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>41</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>47</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="J7" s="14"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="11"/>
-      <c r="O7" s="4"/>
-    </row>
-    <row r="8" ht="17.55" spans="2:15">
+        <v>48</v>
+      </c>
+      <c r="I7" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="K7" s="16"/>
+      <c r="L7" s="17"/>
+      <c r="M7" s="22"/>
+      <c r="N7" s="23"/>
+      <c r="O7" s="24"/>
+      <c r="P7" s="4"/>
+    </row>
+    <row r="8" ht="17.55" spans="2:16">
       <c r="B8" s="4" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C8" t="b">
         <v>1</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>38</v>
+        <v>40</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>41</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="G8" s="10">
+        <v>42</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="H8" s="11">
         <v>5</v>
       </c>
-      <c r="H8" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="I8" s="12">
+      <c r="I8" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="J8" s="18">
         <v>0.5</v>
       </c>
-      <c r="J8" s="7"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="12"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="12"/>
-      <c r="O8" s="4"/>
-    </row>
-    <row r="9" ht="17.55" spans="2:15">
+      <c r="K8" s="7"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="20"/>
+      <c r="N8" s="23"/>
+      <c r="O8" s="25"/>
+      <c r="P8" s="4"/>
+    </row>
+    <row r="9" spans="2:16">
       <c r="B9" s="4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C9" t="b">
         <v>1</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E9" s="10"/>
+        <v>40</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>55</v>
+      </c>
       <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="J9" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="K9" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M9" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="N9" s="1">
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="L9" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="M9" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="N9" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="O9" s="27">
         <v>0.8</v>
       </c>
-      <c r="O9" s="4"/>
-    </row>
-    <row r="10" ht="17.55" spans="2:15">
+      <c r="P9" s="4"/>
+    </row>
+    <row r="10" ht="17.55" spans="2:16">
       <c r="B10" s="4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C10" t="b">
         <v>1</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="E10" s="10"/>
+        <v>40</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>60</v>
+      </c>
       <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="I10" s="12">
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="J10" s="18">
         <v>30</v>
       </c>
-      <c r="J10" s="7"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="12"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="12"/>
-      <c r="O10" s="4"/>
-    </row>
-    <row r="11" ht="17.55" spans="2:15">
+      <c r="K10" s="7"/>
+      <c r="L10" s="17"/>
+      <c r="M10" s="20"/>
+      <c r="N10" s="23"/>
+      <c r="O10" s="25"/>
+      <c r="P10" s="4"/>
+    </row>
+    <row r="11" ht="17.55" spans="2:16">
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
-      <c r="E11" s="12"/>
+      <c r="E11" s="6"/>
       <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="7"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="18"/>
       <c r="K11" s="7"/>
-      <c r="L11" s="12"/>
-      <c r="M11" s="7"/>
-      <c r="N11" s="7"/>
-      <c r="O11" s="7"/>
-    </row>
-    <row r="12" ht="17.55" spans="2:15">
+      <c r="L11" s="21"/>
+      <c r="M11" s="20"/>
+      <c r="N11" s="28"/>
+      <c r="O11" s="28"/>
+      <c r="P11" s="7"/>
+    </row>
+    <row r="12" ht="17.55" spans="2:16">
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
-      <c r="E12" s="12"/>
+      <c r="E12" s="6"/>
       <c r="F12" s="12"/>
       <c r="G12" s="12"/>
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
-      <c r="J12" s="7"/>
+      <c r="J12" s="12"/>
       <c r="K12" s="7"/>
-      <c r="L12" s="12"/>
-      <c r="M12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="12"/>
       <c r="N12" s="7"/>
       <c r="O12" s="7"/>
-    </row>
-    <row r="13" ht="17.55" spans="2:15">
+      <c r="P12" s="7"/>
+    </row>
+    <row r="13" ht="17.55" spans="2:16">
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
-      <c r="E13" s="12"/>
+      <c r="E13" s="6"/>
       <c r="F13" s="12"/>
       <c r="G13" s="12"/>
       <c r="H13" s="12"/>
       <c r="I13" s="12"/>
-      <c r="J13" s="7"/>
+      <c r="J13" s="12"/>
       <c r="K13" s="7"/>
-      <c r="L13" s="12"/>
-      <c r="M13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="12"/>
       <c r="N13" s="7"/>
       <c r="O13" s="7"/>
-    </row>
-    <row r="14" ht="17.55" spans="2:15">
+      <c r="P13" s="7"/>
+    </row>
+    <row r="14" ht="17.55" spans="2:16">
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
-      <c r="E14" s="12"/>
+      <c r="E14" s="6"/>
       <c r="F14" s="12"/>
       <c r="G14" s="12"/>
       <c r="H14" s="12"/>
       <c r="I14" s="12"/>
-      <c r="J14" s="7"/>
+      <c r="J14" s="12"/>
       <c r="K14" s="7"/>
-      <c r="L14" s="12"/>
-      <c r="M14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="12"/>
       <c r="N14" s="7"/>
       <c r="O14" s="7"/>
-    </row>
-    <row r="15" ht="17.55" spans="2:15">
+      <c r="P14" s="7"/>
+    </row>
+    <row r="15" ht="17.55" spans="2:16">
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
-      <c r="E15" s="12"/>
+      <c r="E15" s="6"/>
       <c r="F15" s="12"/>
       <c r="G15" s="12"/>
       <c r="H15" s="12"/>
       <c r="I15" s="12"/>
-      <c r="J15" s="7"/>
+      <c r="J15" s="12"/>
       <c r="K15" s="7"/>
-      <c r="L15" s="12"/>
-      <c r="M15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="12"/>
       <c r="N15" s="7"/>
       <c r="O15" s="7"/>
-    </row>
-    <row r="16" ht="17.55" spans="2:15">
+      <c r="P15" s="7"/>
+    </row>
+    <row r="16" ht="17.55" spans="2:16">
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
-      <c r="E16" s="12"/>
+      <c r="E16" s="6"/>
       <c r="F16" s="12"/>
       <c r="G16" s="12"/>
       <c r="H16" s="12"/>
       <c r="I16" s="12"/>
-      <c r="J16" s="7"/>
+      <c r="J16" s="12"/>
       <c r="K16" s="7"/>
-      <c r="L16" s="12"/>
-      <c r="M16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="12"/>
       <c r="N16" s="7"/>
       <c r="O16" s="7"/>
-    </row>
-    <row r="17" ht="17.55" spans="2:15">
+      <c r="P16" s="7"/>
+    </row>
+    <row r="17" ht="17.55" spans="2:16">
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
-      <c r="E17" s="12"/>
+      <c r="E17" s="6"/>
       <c r="F17" s="12"/>
       <c r="G17" s="12"/>
       <c r="H17" s="12"/>
       <c r="I17" s="12"/>
-      <c r="J17" s="7"/>
+      <c r="J17" s="12"/>
       <c r="K17" s="7"/>
-      <c r="L17" s="12"/>
-      <c r="M17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="12"/>
       <c r="N17" s="7"/>
       <c r="O17" s="7"/>
+      <c r="P17" s="7"/>
     </row>
     <row r="18" ht="17.55" spans="2:2">
       <c r="B18" s="7"/>
